--- a/final_runs/RQ1b_corrector_ablation/corrector_ablation_synthetic_results.xlsx
+++ b/final_runs/RQ1b_corrector_ablation/corrector_ablation_synthetic_results.xlsx
@@ -5505,107 +5505,107 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>F1_Delta_min</t>
+          <t>F1_Delta_count</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>F1_Delta_max</t>
+          <t>Precision_Delta</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta</t>
+          <t>Precision_Delta_std</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta_std</t>
+          <t>Precision_Delta_count</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta_min</t>
+          <t>Recall_Delta</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta_max</t>
+          <t>Recall_Delta_std</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta</t>
+          <t>Recall_Delta_count</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta_std</t>
+          <t>Judge_Score_Delta</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta_min</t>
+          <t>Judge_Score_Delta_std</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta_max</t>
+          <t>Judge_Score_Delta_count</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta</t>
+          <t>Actions_Total_sum</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta_std</t>
+          <t>Actions_Revise_sum</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta_min</t>
+          <t>Actions_Change_sum</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta_max</t>
+          <t>Actions_None_sum</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Total_sum</t>
+          <t>Actions_Error_sum</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Revise_sum</t>
+          <t>Actions_Remove_sum</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Change_sum</t>
+          <t>Actions_Flip_sum</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Actions_None_sum</t>
+          <t>F1_Delta_ci</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Error_sum</t>
+          <t>Precision_Delta_ci</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Remove_sum</t>
+          <t>Recall_Delta_ci</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Flip_sum</t>
+          <t>Judge_Score_Delta_ci</t>
         </is>
       </c>
     </row>
@@ -5627,67 +5627,67 @@
         <v>0.01323518039166825</v>
       </c>
       <c r="E2" t="n">
-        <v>0.134</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1595</v>
+        <v>0.1641</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1641</v>
+        <v>0.04839907023900356</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04839907023900356</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1098</v>
+        <v>0.1173666666666667</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2027</v>
+        <v>0.04526812712420665</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1173666666666667</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04526812712420665</v>
+        <v>0.1857479143663355</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.01220390406198078</v>
       </c>
       <c r="N2" t="n">
-        <v>0.169</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1857479143663355</v>
+        <v>189</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01220390406198078</v>
+        <v>95</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1722488038277511</v>
+        <v>92</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1959997239602507</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.03287801073235416</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.1202299555928719</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.1124522617281562</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.03031617831057381</v>
       </c>
     </row>
     <row r="3">
@@ -5708,67 +5708,67 @@
         <v>0.01815185940888701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06370000000000001</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1</v>
+        <v>0.06176666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06176666666666666</v>
+        <v>0.01240053762275384</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01240053762275384</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0481</v>
+        <v>0.1207666666666667</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0723</v>
+        <v>0.03423395001067409</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1207666666666667</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03423395001067409</v>
+        <v>0.1354179182185915</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.004185174983090172</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1594</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1354179182185915</v>
+        <v>804</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004185174983090172</v>
+        <v>345</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.13109243697479</v>
+        <v>458</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1394470319666985</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>804</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.04509171849544748</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.03080464315427985</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.08504184624263725</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.01039655100563951</v>
       </c>
     </row>
     <row r="4">
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5807,37 +5807,37 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.02804327625116158</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.0433365901483815</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02804327625116158</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0433365901483815</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07795698924731198</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.1076540578849282</v>
       </c>
     </row>
     <row r="5">
@@ -5870,67 +5870,67 @@
         <v>0.01260568654748059</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1024</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1249</v>
+        <v>0.1094</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1094</v>
+        <v>0.01335702062587312</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01335702062587312</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0958</v>
+        <v>0.1267333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1225</v>
+        <v>0.05078280548899729</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1267333333333333</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05078280548899729</v>
+        <v>0.1665056434793275</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0704</v>
+        <v>0.008654637760965436</v>
       </c>
       <c r="N5" t="n">
-        <v>0.169</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1665056434793275</v>
+        <v>189</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008654637760965436</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1574116672800879</v>
+        <v>93</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1746411483253589</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.0313142613347123</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.03318067865294724</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.1261514822221365</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.02149931204328625</v>
       </c>
     </row>
     <row r="6">
@@ -5951,67 +5951,67 @@
         <v>0.02104051647021368</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0675</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1069</v>
+        <v>0.06513333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06513333333333333</v>
+        <v>0.01445072085860541</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01445072085860541</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0485</v>
+        <v>0.1497666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0746</v>
+        <v>0.03719762537223758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1497666666666667</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03719762537223758</v>
+        <v>0.1270308123249304</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1087</v>
+        <v>0.003573487625258868</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1812</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1270308123249304</v>
+        <v>804</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003573487625258868</v>
+        <v>373</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1243697478991604</v>
+        <v>429</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1310924369747908</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>804</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.05226754043771403</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.03589758064639394</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.09240402397359118</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.008877035372268678</v>
       </c>
     </row>
     <row r="7">
@@ -6032,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -6050,37 +6050,37 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.02800388911500025</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.04326854313583937</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02800388911500025</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04326854313583937</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07783882783882801</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.1074850197349025</v>
       </c>
     </row>
     <row r="8">
@@ -6113,67 +6113,67 @@
         <v>0.01662768775266122</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0288</v>
+        <v>0.009466666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009466666666666667</v>
+        <v>0.01639674764498537</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01639674764498537</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0284</v>
+        <v>0.01628127759114745</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0094</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01628127759114745</v>
+        <v>0.1682615629984052</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.009057270088995923</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0282</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1682615629984052</v>
+        <v>189</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009057270088995923</v>
+        <v>78</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.157894736842105</v>
+        <v>102</v>
       </c>
       <c r="R8" t="n">
-        <v>0.174641148325359</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.04130546620508296</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.04073177917445682</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.04044493565914373</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.02249950619330422</v>
       </c>
     </row>
     <row r="9">
@@ -6194,67 +6194,67 @@
         <v>0.02025347706773662</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0457</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0856</v>
+        <v>0.04683333333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04683333333333334</v>
+        <v>0.016274622371451</v>
       </c>
       <c r="H9" t="n">
-        <v>0.016274622371451</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0311</v>
+        <v>0.1159333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0636</v>
+        <v>0.03159055766100582</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1159333333333333</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03159055766100582</v>
+        <v>0.1281149802225355</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.004040774225055709</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1377</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1281149802225355</v>
+        <v>804</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004040774225055709</v>
+        <v>320</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1251556636111127</v>
+        <v>467</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1327186888211987</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>804</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.05031242617741154</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.04042840317691601</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.07847529561995537</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.01003783963700521</v>
       </c>
     </row>
     <row r="10">
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -6284,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -6293,37 +6293,37 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.02805761316872425</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.04336135939630849</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02805761316872425</v>
+        <v>13</v>
       </c>
       <c r="P10" t="n">
-        <v>0.04336135939630849</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.1077155881077946</v>
       </c>
     </row>
   </sheetData>
@@ -6370,107 +6370,107 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>F1_Delta_min</t>
+          <t>F1_Delta_count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>F1_Delta_max</t>
+          <t>Precision_Delta_mean</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta_mean</t>
+          <t>Precision_Delta_std</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta_std</t>
+          <t>Precision_Delta_count</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta_min</t>
+          <t>Recall_Delta_mean</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Precision_Delta_max</t>
+          <t>Recall_Delta_std</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta_mean</t>
+          <t>Recall_Delta_count</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta_std</t>
+          <t>Judge_Score_Delta_mean</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta_min</t>
+          <t>Judge_Score_Delta_std</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Recall_Delta_max</t>
+          <t>Judge_Score_Delta_count</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta_mean</t>
+          <t>Actions_Total_sum_sum</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta_std</t>
+          <t>Actions_Revise_sum_sum</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta_min</t>
+          <t>Actions_Change_sum_sum</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Judge_Score_Delta_max</t>
+          <t>Actions_None_sum_sum</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Total_sum_sum</t>
+          <t>Actions_Error_sum_sum</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Revise_sum_sum</t>
+          <t>Actions_Remove_sum_sum</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Change_sum_sum</t>
+          <t>Actions_Flip_sum_sum</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Actions_None_sum_sum</t>
+          <t>F1_Delta_ci</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Error_sum_sum</t>
+          <t>Precision_Delta_ci</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Remove_sum_sum</t>
+          <t>Recall_Delta_ci</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Actions_Flip_sum_sum</t>
+          <t>Judge_Score_Delta_ci</t>
         </is>
       </c>
     </row>
@@ -6487,67 +6487,67 @@
         <v>0.0725511084224999</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1447</v>
+        <v>0.07528888888888889</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07528888888888889</v>
+        <v>0.0828814838813252</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0828814838813252</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.07937777777777778</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1641</v>
+        <v>0.06876418910816666</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07937777777777778</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06876418910816666</v>
+        <v>0.1164030362786962</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.08055347616428858</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1207666666666667</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1164030362786962</v>
+        <v>1006</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08055347616428858</v>
+        <v>450</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02804327625116158</v>
+        <v>553</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1857479143663355</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1006</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>553</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.1802269444593856</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2058890197128756</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.1708197153794112</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.2001059279498108</v>
       </c>
     </row>
     <row r="3">
@@ -6563,67 +6563,67 @@
         <v>0.06149269152599445</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1169333333333333</v>
+        <v>0.05817777777777777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05817777777777777</v>
+        <v>0.05503067158244404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05503067158244404</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.09216666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1094</v>
+        <v>0.08064523820068017</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09216666666666667</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08064523820068017</v>
+        <v>0.1071801149730861</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.07135279692846666</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1497666666666667</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1071801149730861</v>
+        <v>1006</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07135279692846666</v>
+        <v>471</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02800388911500025</v>
+        <v>524</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1665056434793275</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1006</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>471</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.1527563140148598</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1367037665792024</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2003338774849154</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.1772501736866706</v>
       </c>
     </row>
     <row r="4">
@@ -6639,67 +6639,67 @@
         <v>0.03661210081279038</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06766666666666667</v>
+        <v>0.01876666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01876666666666667</v>
+        <v>0.02476303248347782</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02476303248347782</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.04177777777777778</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04683333333333334</v>
+        <v>0.064392350592402</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04177777777777778</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.064392350592402</v>
+        <v>0.108144718796555</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.07220384610965974</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1159333333333333</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.108144718796555</v>
+        <v>1006</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07220384610965974</v>
+        <v>408</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02805761316872425</v>
+        <v>571</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1682615629984052</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1006</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.09094950033433041</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.06151478284874338</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1599594664528522</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.1793642970522004</v>
       </c>
     </row>
   </sheetData>
